--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260624.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260624.xlsx
@@ -1195,17 +1195,17 @@
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>凱基金</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>64,158,698</t>
+          <t>334,612,639</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1217,17 +1217,17 @@
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>凱基金</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>334,612,639</t>
+          <t>64,158,698</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>第一金</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>237,973,115</t>
+          <t>3,798,627</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2892</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>第一金</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>23,103,314</t>
+          <t>237,973,115</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1459,17 +1459,17 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>3,798,627</t>
+          <t>23,103,314</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1481,17 +1481,17 @@
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2880</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>華南金</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1,676,125</t>
+          <t>195,326,723</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -1503,17 +1503,17 @@
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2880</t>
+          <t>3661</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>華南金</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>195,326,723</t>
+          <t>1,676,125</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -1613,17 +1613,17 @@
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>長榮</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>23,082,423</t>
+          <t>4,551,368</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>長榮</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>4,551,368</t>
+          <t>23,082,423</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
